--- a/data/dividends_info_20260807.xlsx
+++ b/data/dividends_info_20260807.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>46.8650016784668</v>
+        <v>48.26499938964844</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1920409618620638</v>
+        <v>0.1864705296552902</v>
       </c>
       <c r="J2" t="n">
         <v>220</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4799999892711639</v>
+        <v>0.4900000095367432</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8333333519597853</v>
+        <v>0.8163265147242933</v>
       </c>
       <c r="J5" t="n">
         <v>129</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>46.8650016784668</v>
+        <v>48.26499938964844</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1920409618620638</v>
+        <v>0.1864705296552902</v>
       </c>
       <c r="J6" t="n">
         <v>129</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.144999980926514</v>
+        <v>2.150000095367432</v>
       </c>
       <c r="I7" t="n">
-        <v>3.589743621663835</v>
+        <v>3.58139518997746</v>
       </c>
       <c r="J7" t="n">
         <v>108</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.34000015258789</v>
+        <v>23.28000068664551</v>
       </c>
       <c r="I8" t="n">
-        <v>1.156812331768828</v>
+        <v>1.159793780224777</v>
       </c>
       <c r="J8" t="n">
         <v>108</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>23.02000045776367</v>
+        <v>23.13999938964844</v>
       </c>
       <c r="I9" t="n">
-        <v>2.56298865450725</v>
+        <v>2.549697560769745</v>
       </c>
       <c r="J9" t="n">
         <v>108</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5.989999771118164</v>
+        <v>5.900000095367432</v>
       </c>
       <c r="I10" t="n">
-        <v>3.338898291187508</v>
+        <v>3.389830453681454</v>
       </c>
       <c r="J10" t="n">
         <v>101</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>9.829999923706055</v>
+        <v>10.09000015258789</v>
       </c>
       <c r="I11" t="n">
-        <v>4.67955242696048</v>
+        <v>4.558969207567543</v>
       </c>
       <c r="J11" t="n">
         <v>80</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7.75</v>
+        <v>7.800000190734863</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7741935483870968</v>
+        <v>0.7692307504206254</v>
       </c>
       <c r="J12" t="n">
         <v>73</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.4620000123977661</v>
+        <v>0.4900000095367432</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8658008425671074</v>
+        <v>0.8163265147242933</v>
       </c>
       <c r="J13" t="n">
         <v>73</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5.699999809265137</v>
+        <v>5.599999904632568</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8771930118089981</v>
+        <v>0.8928571580624097</v>
       </c>
       <c r="J14" t="n">
         <v>59</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4.949999809265137</v>
+        <v>5.099999904632568</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7676767972571169</v>
+        <v>0.7450980531486446</v>
       </c>
       <c r="J15" t="n">
         <v>52</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>23.34000015258789</v>
+        <v>23.28000068664551</v>
       </c>
       <c r="I16" t="n">
-        <v>1.156812331768828</v>
+        <v>1.159793780224777</v>
       </c>
       <c r="J16" t="n">
         <v>45</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.980000019073486</v>
+        <v>1.99399995803833</v>
       </c>
       <c r="I17" t="n">
-        <v>2.878787851056303</v>
+        <v>2.858575787337319</v>
       </c>
       <c r="J17" t="n">
         <v>45</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>46.8650016784668</v>
+        <v>48.26499938964844</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1920409618620638</v>
+        <v>0.1864705296552902</v>
       </c>
       <c r="J18" t="n">
         <v>45</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>99.55000305175781</v>
+        <v>98.5</v>
       </c>
       <c r="I19" t="n">
-        <v>1.336012013287945</v>
+        <v>1.350253807106599</v>
       </c>
       <c r="J19" t="n">
         <v>45</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5.71999979019165</v>
+        <v>5.659999847412109</v>
       </c>
       <c r="I20" t="n">
-        <v>5.244755437131728</v>
+        <v>5.300353499782643</v>
       </c>
       <c r="J20" t="n">
         <v>38</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.4620000123977661</v>
+        <v>0.4900000095367432</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8658008425671074</v>
+        <v>0.8163265147242933</v>
       </c>
       <c r="J21" t="n">
         <v>17</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>3.059999942779541</v>
       </c>
       <c r="I22" t="n">
-        <v>7.333333333333333</v>
+        <v>7.189542618100957</v>
       </c>
       <c r="J22" t="n">
         <v>3</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>4.949999809265137</v>
+        <v>5.099999904632568</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7676767972571169</v>
+        <v>0.7450980531486446</v>
       </c>
       <c r="J23" t="n">
         <v>-4</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2.650000095367432</v>
+        <v>2.690000057220459</v>
       </c>
       <c r="I25" t="n">
-        <v>5.583735648110744</v>
+        <v>5.500706202694077</v>
       </c>
       <c r="J25" t="n">
         <v>-4</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5.75</v>
+        <v>5.829999923706055</v>
       </c>
       <c r="I26" t="n">
-        <v>4.347826086956522</v>
+        <v>4.288164721639967</v>
       </c>
       <c r="J26" t="n">
         <v>-11</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4.210000038146973</v>
+        <v>4.190000057220459</v>
       </c>
       <c r="I27" t="n">
-        <v>3.325415646827901</v>
+        <v>3.34128873718614</v>
       </c>
       <c r="J27" t="n">
         <v>-18</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>9.913000106811523</v>
+        <v>10.04399967193604</v>
       </c>
       <c r="I28" t="n">
-        <v>2.622818492873274</v>
+        <v>2.588610200042784</v>
       </c>
       <c r="J28" t="n">
         <v>-18</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>13.72000026702881</v>
+        <v>13.97999954223633</v>
       </c>
       <c r="I29" t="n">
-        <v>4.373177757451571</v>
+        <v>4.291845634095209</v>
       </c>
       <c r="J29" t="n">
         <v>-18</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.697999954223633</v>
+        <v>2.700000047683716</v>
       </c>
       <c r="I30" t="n">
-        <v>8.154188425970766</v>
+        <v>8.148148004246677</v>
       </c>
       <c r="J30" t="n">
         <v>-18</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.4620000123977661</v>
+        <v>0.4900000095367432</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8658008425671074</v>
+        <v>0.8163265147242933</v>
       </c>
       <c r="J31" t="n">
         <v>-18</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>6.53000020980835</v>
+        <v>6.550000190734863</v>
       </c>
       <c r="I32" t="n">
-        <v>1.531393518943469</v>
+        <v>1.526717512794159</v>
       </c>
       <c r="J32" t="n">
         <v>-18</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>19.04999923706055</v>
+        <v>18.39999961853027</v>
       </c>
       <c r="I33" t="n">
-        <v>1.973753359887365</v>
+        <v>2.04347830323506</v>
       </c>
       <c r="J33" t="n">
         <v>-18</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>5.670000076293945</v>
+        <v>5.659999847412109</v>
       </c>
       <c r="I35" t="n">
-        <v>2.116402087924397</v>
+        <v>2.120141399913057</v>
       </c>
       <c r="J35" t="n">
         <v>-25</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>2.799999952316284</v>
+        <v>2.900000095367432</v>
       </c>
       <c r="I37" t="n">
-        <v>5.357142948374458</v>
+        <v>5.172413623006964</v>
       </c>
       <c r="J37" t="n">
         <v>-25</v>
@@ -2596,146 +2596,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>F.I.L.A. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0004967292</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-10-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>9.829999923706055</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>4.67955242696048</v>
-      </c>
-      <c r="I2" t="n">
-        <v>80</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>TENARIS S.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>LU2598331598</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-11-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-11-25</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>23.02000045776367</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>DOLLARI USA</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2.56298865450725</v>
-      </c>
-      <c r="I3" t="n">
-        <v>108</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
